--- a/notebooks/results/excel/current/Q3_reduced_current__tot=6_flex=0.1_xcfe=60.xlsx
+++ b/notebooks/results/excel/current/Q3_reduced_current__tot=6_flex=0.1_xcfe=60.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marta/Documents/MSc CAM/Dissertation/PyPSA-GB/notebooks/results/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marta/Documents/MSc CAM/Dissertation/PyPSA-GB/notebooks/results/excel/current/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3809367-4E44-A24A-B624-DDC5069159C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72753091-61D6-E24C-99CD-82786A620872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10260" yWindow="700" windowWidth="20620" windowHeight="17400" xr2:uid="{D4188A73-9F76-7B43-A2AE-82D891E862BC}"/>
+    <workbookView xWindow="9620" yWindow="660" windowWidth="20620" windowHeight="17400" xr2:uid="{D4188A73-9F76-7B43-A2AE-82D891E862BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="8" r:id="rId1"/>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>Total Solar PV Curtailment Reduction</t>
-  </si>
-  <si>
-    <t>Scotland</t>
   </si>
   <si>
     <t>Hydrogen Gas</t>
@@ -279,6 +276,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Current</t>
   </si>
 </sst>
 </file>
@@ -768,7 +768,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -776,7 +776,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1"/>
     </row>
@@ -794,7 +794,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="6">
-        <v>0.03</v>
+        <v>0.6</v>
       </c>
       <c r="D6" s="1"/>
     </row>
@@ -1015,10 +1015,10 @@
         <v>87546565.338318497</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1282,48 +1282,48 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C1" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="10">
         <v>372.43929000000003</v>
@@ -1362,7 +1362,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="12"/>
       <c r="B3" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="10">
         <v>1642.8915400000001</v>
@@ -1401,7 +1401,7 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="12"/>
       <c r="B4" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" s="10">
         <v>9185.8067100000007</v>
@@ -1440,7 +1440,7 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="10">
         <v>23586</v>
@@ -1479,7 +1479,7 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="12"/>
       <c r="B6" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="10">
         <v>3534.0360000000001</v>
@@ -1518,7 +1518,7 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="12"/>
       <c r="B7" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="10">
         <v>13695</v>
@@ -1560,7 +1560,7 @@
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="10">
         <v>4067.2939999999999</v>
@@ -1599,7 +1599,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="10">
         <v>11</v>
@@ -1641,7 +1641,7 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="12"/>
       <c r="B10" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="10">
         <v>834.51107000000002</v>
@@ -1683,7 +1683,7 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="12"/>
       <c r="B11" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="10">
         <v>1897.296</v>
@@ -1725,7 +1725,7 @@
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="12"/>
       <c r="B12" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="10">
         <v>48629.190949999997</v>
@@ -1764,7 +1764,7 @@
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="12"/>
       <c r="B13" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="10">
         <v>254.358</v>
@@ -1806,7 +1806,7 @@
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="12"/>
       <c r="B14" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="10">
         <v>4570</v>
@@ -1848,7 +1848,7 @@
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="12"/>
       <c r="B15" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="10">
         <v>53544.201999999997</v>
@@ -1890,7 +1890,7 @@
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="12"/>
       <c r="B16" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="10">
         <v>78.5</v>
@@ -1929,7 +1929,7 @@
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="12"/>
       <c r="B17" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="10">
         <v>27270.741000000002</v>
@@ -1971,7 +1971,7 @@
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="12"/>
       <c r="B18" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="10">
         <v>3662.89</v>
@@ -2010,7 +2010,7 @@
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="12"/>
       <c r="B19" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="10">
         <v>55.819389999999999</v>
@@ -2049,7 +2049,7 @@
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="12"/>
       <c r="B20" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="10">
         <v>40470.421999999999</v>
@@ -2091,7 +2091,7 @@
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>
       <c r="B21" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="10">
         <v>4643.1779999999999</v>
@@ -2129,10 +2129,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="10">
         <v>230800</v>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="10">
         <v>12450</v>
@@ -2218,7 +2218,7 @@
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="12"/>
       <c r="B24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" s="10">
         <v>3653.0947500000002</v>
@@ -2257,7 +2257,7 @@
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
       <c r="B25" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="10">
         <v>278.38099999999997</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="10">
         <v>0</v>
@@ -2337,7 +2337,7 @@
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="12"/>
       <c r="B27" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="10">
         <v>0</v>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="10">
         <v>26471.973000000002</v>
@@ -2420,7 +2420,7 @@
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="12"/>
       <c r="B29" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="10">
         <v>857.70799999999997</v>
@@ -2462,7 +2462,7 @@
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="12"/>
       <c r="B30" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" s="10">
         <v>457.99400000000003</v>
@@ -2504,7 +2504,7 @@
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="12"/>
       <c r="B31" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="10">
         <v>5300</v>
@@ -2545,10 +2545,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C32" s="10">
         <v>46768.008000000002</v>
@@ -2605,48 +2605,48 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C1" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="10">
         <v>372.43929000000003</v>
@@ -2685,7 +2685,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="12"/>
       <c r="B3" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="10">
         <v>1642.8915400000001</v>
@@ -2724,7 +2724,7 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="12"/>
       <c r="B4" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" s="10">
         <v>9185.8067100000007</v>
@@ -2763,7 +2763,7 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="10">
         <v>23586</v>
@@ -2802,7 +2802,7 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="12"/>
       <c r="B6" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="10">
         <v>3534.0360000000001</v>
@@ -2841,7 +2841,7 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="12"/>
       <c r="B7" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="10">
         <v>13695</v>
@@ -2883,7 +2883,7 @@
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="10">
         <v>4067.2939999999999</v>
@@ -2922,7 +2922,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="10">
         <v>11</v>
@@ -2964,7 +2964,7 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="12"/>
       <c r="B10" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="10">
         <v>834.51107000000002</v>
@@ -3006,7 +3006,7 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="12"/>
       <c r="B11" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="10">
         <v>1897.296</v>
@@ -3048,7 +3048,7 @@
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="12"/>
       <c r="B12" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="10">
         <v>48629.190949999997</v>
@@ -3087,7 +3087,7 @@
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="12"/>
       <c r="B13" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="10">
         <v>254.358</v>
@@ -3129,7 +3129,7 @@
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="12"/>
       <c r="B14" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="10">
         <v>4570</v>
@@ -3171,7 +3171,7 @@
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="12"/>
       <c r="B15" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="10">
         <v>53544.201999999997</v>
@@ -3213,7 +3213,7 @@
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="12"/>
       <c r="B16" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="10">
         <v>78.5</v>
@@ -3252,7 +3252,7 @@
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="12"/>
       <c r="B17" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="10">
         <v>27270.741000000002</v>
@@ -3294,7 +3294,7 @@
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="12"/>
       <c r="B18" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="10">
         <v>3662.89</v>
@@ -3333,7 +3333,7 @@
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="12"/>
       <c r="B19" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="10">
         <v>55.819389999999999</v>
@@ -3372,7 +3372,7 @@
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="12"/>
       <c r="B20" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="10">
         <v>40470.421999999999</v>
@@ -3414,7 +3414,7 @@
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>
       <c r="B21" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="10">
         <v>4643.1779999999999</v>
@@ -3452,10 +3452,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="10">
         <v>230800</v>
@@ -3496,10 +3496,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="10">
         <v>12450</v>
@@ -3541,7 +3541,7 @@
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="12"/>
       <c r="B24" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="10">
         <v>32000000</v>
@@ -3583,7 +3583,7 @@
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
       <c r="B25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" s="10">
         <v>3653.0947500000002</v>
@@ -3622,7 +3622,7 @@
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="12"/>
       <c r="B26" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" s="10">
         <v>278.38099999999997</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="10">
         <v>0</v>
@@ -3702,7 +3702,7 @@
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="12"/>
       <c r="B28" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28" s="10">
         <v>0</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29" s="10">
         <v>26471.973000000002</v>
@@ -3785,7 +3785,7 @@
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="12"/>
       <c r="B30" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="10">
         <v>857.70799999999997</v>
@@ -3827,7 +3827,7 @@
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="12"/>
       <c r="B31" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C31" s="10">
         <v>457.99400000000003</v>
@@ -3869,7 +3869,7 @@
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="12"/>
       <c r="B32" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32" s="10">
         <v>5300</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C33" s="10">
         <v>16000000</v>
@@ -3952,7 +3952,7 @@
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="12"/>
       <c r="B34" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C34" s="10">
         <v>46768.008000000002</v>
@@ -4010,48 +4010,48 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C1" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="10">
         <v>372.43929000000003</v>
@@ -4090,7 +4090,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="12"/>
       <c r="B3" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="10">
         <v>1642.8915400000001</v>
@@ -4129,7 +4129,7 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="12"/>
       <c r="B4" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" s="10">
         <v>9185.8067100000007</v>
@@ -4168,7 +4168,7 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="10">
         <v>23586</v>
@@ -4207,7 +4207,7 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="12"/>
       <c r="B6" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="10">
         <v>3534.0360000000001</v>
@@ -4246,7 +4246,7 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="12"/>
       <c r="B7" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="10">
         <v>13695</v>
@@ -4288,7 +4288,7 @@
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="10">
         <v>4067.2939999999999</v>
@@ -4327,7 +4327,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="10">
         <v>11</v>
@@ -4369,7 +4369,7 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="12"/>
       <c r="B10" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="10">
         <v>834.51107000000002</v>
@@ -4411,7 +4411,7 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="12"/>
       <c r="B11" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="10">
         <v>1897.296</v>
@@ -4453,7 +4453,7 @@
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="12"/>
       <c r="B12" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="10">
         <v>48629.190949999997</v>
@@ -4492,7 +4492,7 @@
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="12"/>
       <c r="B13" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="10">
         <v>254.358</v>
@@ -4534,7 +4534,7 @@
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="12"/>
       <c r="B14" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="10">
         <v>4570</v>
@@ -4576,7 +4576,7 @@
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="12"/>
       <c r="B15" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="10">
         <v>53544.201999999997</v>
@@ -4618,7 +4618,7 @@
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="12"/>
       <c r="B16" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="10">
         <v>78.5</v>
@@ -4657,7 +4657,7 @@
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="12"/>
       <c r="B17" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="10">
         <v>27270.741000000002</v>
@@ -4699,7 +4699,7 @@
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="12"/>
       <c r="B18" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="10">
         <v>3662.89</v>
@@ -4738,7 +4738,7 @@
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="12"/>
       <c r="B19" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="10">
         <v>55.819389999999999</v>
@@ -4777,7 +4777,7 @@
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="12"/>
       <c r="B20" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="10">
         <v>40470.421999999999</v>
@@ -4819,7 +4819,7 @@
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>
       <c r="B21" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="10">
         <v>4643.1779999999999</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="10">
         <v>230800</v>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="10">
         <v>12450</v>
@@ -4946,7 +4946,7 @@
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="12"/>
       <c r="B24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" s="10">
         <v>3653.0947500000002</v>
@@ -4985,7 +4985,7 @@
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
       <c r="B25" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="10">
         <v>278.38099999999997</v>
@@ -5024,7 +5024,7 @@
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="12"/>
       <c r="B26" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C26" s="10">
         <v>240000000</v>
@@ -5065,10 +5065,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="10">
         <v>0</v>
@@ -5107,7 +5107,7 @@
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="12"/>
       <c r="B28" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28" s="10">
         <v>0</v>
@@ -5145,10 +5145,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29" s="10">
         <v>26471.973000000002</v>
@@ -5190,7 +5190,7 @@
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="12"/>
       <c r="B30" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="10">
         <v>857.70799999999997</v>
@@ -5232,7 +5232,7 @@
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="12"/>
       <c r="B31" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C31" s="10">
         <v>457.99400000000003</v>
@@ -5274,7 +5274,7 @@
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="12"/>
       <c r="B32" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32" s="10">
         <v>5300</v>
@@ -5315,10 +5315,10 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C33" s="10">
         <v>46768.008000000002</v>
@@ -5375,48 +5375,48 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C1" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="10">
         <v>372.43929000000003</v>
@@ -5455,7 +5455,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="12"/>
       <c r="B3" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="10">
         <v>1642.8915400000001</v>
@@ -5494,7 +5494,7 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="12"/>
       <c r="B4" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" s="10">
         <v>9185.8067100000007</v>
@@ -5533,7 +5533,7 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="10">
         <v>23586</v>
@@ -5572,7 +5572,7 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="12"/>
       <c r="B6" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="10">
         <v>3534.0360000000001</v>
@@ -5611,7 +5611,7 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="12"/>
       <c r="B7" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="10">
         <v>13695</v>
@@ -5653,7 +5653,7 @@
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="10">
         <v>4067.2939999999999</v>
@@ -5692,7 +5692,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="10">
         <v>11</v>
@@ -5734,7 +5734,7 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="12"/>
       <c r="B10" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="10">
         <v>834.51107000000002</v>
@@ -5776,7 +5776,7 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="12"/>
       <c r="B11" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="10">
         <v>1897.296</v>
@@ -5818,7 +5818,7 @@
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="12"/>
       <c r="B12" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="10">
         <v>48629.190949999997</v>
@@ -5857,7 +5857,7 @@
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="12"/>
       <c r="B13" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="10">
         <v>254.358</v>
@@ -5899,7 +5899,7 @@
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="12"/>
       <c r="B14" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="10">
         <v>4570</v>
@@ -5941,7 +5941,7 @@
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="12"/>
       <c r="B15" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="10">
         <v>53544.201999999997</v>
@@ -5983,7 +5983,7 @@
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="12"/>
       <c r="B16" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="10">
         <v>78.5</v>
@@ -6022,7 +6022,7 @@
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="12"/>
       <c r="B17" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="10">
         <v>27270.741000000002</v>
@@ -6064,7 +6064,7 @@
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="12"/>
       <c r="B18" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="10">
         <v>3662.89</v>
@@ -6103,7 +6103,7 @@
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="12"/>
       <c r="B19" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="10">
         <v>55.819389999999999</v>
@@ -6142,7 +6142,7 @@
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="12"/>
       <c r="B20" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="10">
         <v>40470.421999999999</v>
@@ -6184,7 +6184,7 @@
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>
       <c r="B21" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="10">
         <v>4643.1779999999999</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="10">
         <v>230800</v>
@@ -6266,10 +6266,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="10">
         <v>12450</v>
@@ -6311,7 +6311,7 @@
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="12"/>
       <c r="B24" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="10">
         <v>32000000</v>
@@ -6353,7 +6353,7 @@
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
       <c r="B25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" s="10">
         <v>3653.0947500000002</v>
@@ -6392,7 +6392,7 @@
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="12"/>
       <c r="B26" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" s="10">
         <v>278.38099999999997</v>
@@ -6431,7 +6431,7 @@
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="12"/>
       <c r="B27" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27" s="10">
         <v>240000000</v>
@@ -6472,10 +6472,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="10">
         <v>0</v>
@@ -6514,7 +6514,7 @@
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="12"/>
       <c r="B29" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" s="10">
         <v>0</v>
@@ -6552,10 +6552,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" s="10">
         <v>26471.973000000002</v>
@@ -6597,7 +6597,7 @@
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="12"/>
       <c r="B31" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" s="10">
         <v>857.70799999999997</v>
@@ -6639,7 +6639,7 @@
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="12"/>
       <c r="B32" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C32" s="10">
         <v>457.99400000000003</v>
@@ -6681,7 +6681,7 @@
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="12"/>
       <c r="B33" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C33" s="10">
         <v>5300</v>
@@ -6722,10 +6722,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C34" s="10">
         <v>16000000</v>
@@ -6764,7 +6764,7 @@
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="12"/>
       <c r="B35" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C35" s="10">
         <v>46768.008000000002</v>
@@ -6822,45 +6822,45 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C1" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="10">
         <v>0</v>
@@ -6899,7 +6899,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="12"/>
       <c r="B3" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="10">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="12"/>
       <c r="B4" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" s="10">
         <v>0</v>
@@ -6977,7 +6977,7 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
@@ -7016,7 +7016,7 @@
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="12"/>
       <c r="B6" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
@@ -7055,7 +7055,7 @@
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="12"/>
       <c r="B7" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="10">
         <v>0</v>
@@ -7094,7 +7094,7 @@
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="10">
         <v>0</v>
@@ -7172,7 +7172,7 @@
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="12"/>
       <c r="B10" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="10">
         <v>0</v>
@@ -7211,7 +7211,7 @@
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="12"/>
       <c r="B11" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="10">
         <v>0</v>
@@ -7250,7 +7250,7 @@
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="12"/>
       <c r="B12" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="10">
         <v>0</v>
@@ -7289,7 +7289,7 @@
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="12"/>
       <c r="B13" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -7328,7 +7328,7 @@
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="12"/>
       <c r="B14" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="10">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="12"/>
       <c r="B15" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="10">
         <v>0</v>
@@ -7406,7 +7406,7 @@
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="12"/>
       <c r="B16" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -7445,7 +7445,7 @@
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="12"/>
       <c r="B17" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="10">
         <v>0</v>
@@ -7484,7 +7484,7 @@
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="12"/>
       <c r="B18" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="10">
         <v>0</v>
@@ -7523,7 +7523,7 @@
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="12"/>
       <c r="B19" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="10">
         <v>0</v>
@@ -7562,7 +7562,7 @@
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="12"/>
       <c r="B20" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="10">
         <v>0</v>
@@ -7601,7 +7601,7 @@
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>
       <c r="B21" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="10">
         <v>0</v>
@@ -7639,10 +7639,10 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="10">
         <v>0</v>
@@ -7680,10 +7680,10 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="10">
         <v>0</v>
@@ -7722,7 +7722,7 @@
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="12"/>
       <c r="B24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" s="10">
         <v>0</v>
@@ -7761,7 +7761,7 @@
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
       <c r="B25" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="10">
         <v>0</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C26" s="10">
         <v>0</v>
@@ -7841,7 +7841,7 @@
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="12"/>
       <c r="B27" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" s="10">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="12"/>
       <c r="B28" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28" s="10">
         <v>0</v>
@@ -7919,7 +7919,7 @@
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="12"/>
       <c r="B29" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="10">
         <v>0</v>
@@ -7957,10 +7957,10 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C30" s="10">
         <v>0</v>
@@ -8016,45 +8016,45 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C1" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="10">
         <v>0</v>
@@ -8093,7 +8093,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="12"/>
       <c r="B3" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="10">
         <v>0</v>
@@ -8132,7 +8132,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="12"/>
       <c r="B4" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" s="10">
         <v>0</v>
@@ -8171,7 +8171,7 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
@@ -8210,7 +8210,7 @@
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="12"/>
       <c r="B6" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
@@ -8249,7 +8249,7 @@
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="12"/>
       <c r="B7" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="10">
         <v>0</v>
@@ -8288,7 +8288,7 @@
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
@@ -8327,7 +8327,7 @@
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="10">
         <v>0</v>
@@ -8366,7 +8366,7 @@
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="12"/>
       <c r="B10" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="10">
         <v>0</v>
@@ -8405,7 +8405,7 @@
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="12"/>
       <c r="B11" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="10">
         <v>0</v>
@@ -8444,7 +8444,7 @@
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="12"/>
       <c r="B12" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="10">
         <v>0</v>
@@ -8483,7 +8483,7 @@
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="12"/>
       <c r="B13" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -8522,7 +8522,7 @@
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="12"/>
       <c r="B14" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="10">
         <v>0</v>
@@ -8561,7 +8561,7 @@
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="12"/>
       <c r="B15" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="10">
         <v>0</v>
@@ -8600,7 +8600,7 @@
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="12"/>
       <c r="B16" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -8639,7 +8639,7 @@
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="12"/>
       <c r="B17" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="10">
         <v>0</v>
@@ -8678,7 +8678,7 @@
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="12"/>
       <c r="B18" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="10">
         <v>0</v>
@@ -8717,7 +8717,7 @@
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="12"/>
       <c r="B19" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="10">
         <v>0</v>
@@ -8756,7 +8756,7 @@
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="12"/>
       <c r="B20" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="10">
         <v>0</v>
@@ -8795,7 +8795,7 @@
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>
       <c r="B21" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="10">
         <v>0</v>
@@ -8833,10 +8833,10 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="10">
         <v>0</v>
@@ -8874,10 +8874,10 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="10">
         <v>0</v>
@@ -8916,7 +8916,7 @@
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="12"/>
       <c r="B24" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="10">
         <v>0</v>
@@ -8955,7 +8955,7 @@
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
       <c r="B25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" s="10">
         <v>0</v>
@@ -8994,7 +8994,7 @@
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="12"/>
       <c r="B26" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" s="10">
         <v>0</v>
@@ -9033,7 +9033,7 @@
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="12"/>
       <c r="B27" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27" s="10">
         <v>0</v>
@@ -9071,10 +9071,10 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="10">
         <v>0</v>
@@ -9113,7 +9113,7 @@
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="12"/>
       <c r="B29" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="10">
         <v>0</v>
@@ -9152,7 +9152,7 @@
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="12"/>
       <c r="B30" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" s="10">
         <v>0</v>
@@ -9191,7 +9191,7 @@
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="12"/>
       <c r="B31" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="10">
         <v>0</v>
@@ -9229,10 +9229,10 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C32" s="10">
         <v>0</v>
@@ -9271,7 +9271,7 @@
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="12"/>
       <c r="B33" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C33" s="10">
         <v>0</v>
